--- a/results/model_comparison.xlsx
+++ b/results/model_comparison.xlsx
@@ -1,34 +1,226 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+  <si>
+    <t>experiment_name</t>
+  </si>
+  <si>
+    <t>accuracy</t>
+  </si>
+  <si>
+    <t>balanced_accuracy</t>
+  </si>
+  <si>
+    <t>precision_macro</t>
+  </si>
+  <si>
+    <t>recall_macro</t>
+  </si>
+  <si>
+    <t>f1_macro</t>
+  </si>
+  <si>
+    <t>precision_weighted</t>
+  </si>
+  <si>
+    <t>recall_weighted</t>
+  </si>
+  <si>
+    <t>f1_weighted</t>
+  </si>
+  <si>
+    <t>specificity_macro</t>
+  </si>
+  <si>
+    <t>top_2_accuracy</t>
+  </si>
+  <si>
+    <t>top_3_accuracy</t>
+  </si>
+  <si>
+    <t>mcc</t>
+  </si>
+  <si>
+    <t>cohen_kappa</t>
+  </si>
+  <si>
+    <t>auc_macro_ovr</t>
+  </si>
+  <si>
+    <t>inference_total_seconds</t>
+  </si>
+  <si>
+    <t>inference_ms_per_image</t>
+  </si>
+  <si>
+    <t>num_parameters</t>
+  </si>
+  <si>
+    <t>custom_cnn_fine_tuning_aug</t>
+  </si>
+  <si>
+    <t>custom_cnn_fine_tuning_noaug</t>
+  </si>
+  <si>
+    <t>custom_cnn_scratch_aug</t>
+  </si>
+  <si>
+    <t>custom_cnn_scratch_noaug</t>
+  </si>
+  <si>
+    <t>custom_cnn_transfer_aug</t>
+  </si>
+  <si>
+    <t>custom_cnn_transfer_noaug</t>
+  </si>
+  <si>
+    <t>densenet121_fine_tuning_aug</t>
+  </si>
+  <si>
+    <t>densenet121_fine_tuning_noaug</t>
+  </si>
+  <si>
+    <t>densenet121_scratch_aug</t>
+  </si>
+  <si>
+    <t>densenet121_scratch_noaug</t>
+  </si>
+  <si>
+    <t>densenet121_transfer_aug</t>
+  </si>
+  <si>
+    <t>densenet121_transfer_noaug</t>
+  </si>
+  <si>
+    <t>efficientnetb0_fine_tuning_aug</t>
+  </si>
+  <si>
+    <t>efficientnetb0_fine_tuning_noaug</t>
+  </si>
+  <si>
+    <t>efficientnetb0_scratch_aug</t>
+  </si>
+  <si>
+    <t>efficientnetb0_scratch_noaug</t>
+  </si>
+  <si>
+    <t>efficientnetb0_transfer_aug</t>
+  </si>
+  <si>
+    <t>efficientnetb0_transfer_noaug</t>
+  </si>
+  <si>
+    <t>mobilenetv2_fine_tuning_aug</t>
+  </si>
+  <si>
+    <t>mobilenetv2_fine_tuning_noaug</t>
+  </si>
+  <si>
+    <t>mobilenetv2_scratch_aug</t>
+  </si>
+  <si>
+    <t>mobilenetv2_scratch_noaug</t>
+  </si>
+  <si>
+    <t>mobilenetv2_transfer_aug</t>
+  </si>
+  <si>
+    <t>mobilenetv2_transfer_noaug</t>
+  </si>
+  <si>
+    <t>poster_v2_fine_tuning_aug</t>
+  </si>
+  <si>
+    <t>poster_v2_scratch_aug</t>
+  </si>
+  <si>
+    <t>poster_v2_scratch_noaug</t>
+  </si>
+  <si>
+    <t>poster_v2_transfer_aug</t>
+  </si>
+  <si>
+    <t>qcs_fine_tuning_aug</t>
+  </si>
+  <si>
+    <t>qcs_fine_tuning_noaug</t>
+  </si>
+  <si>
+    <t>qcs_scratch_aug</t>
+  </si>
+  <si>
+    <t>qcs_scratch_noaug</t>
+  </si>
+  <si>
+    <t>qcs_transfer_aug</t>
+  </si>
+  <si>
+    <t>qcs_transfer_noaug</t>
+  </si>
+  <si>
+    <t>resnet50_fine_tuning_aug</t>
+  </si>
+  <si>
+    <t>resnet50_fine_tuning_noaug</t>
+  </si>
+  <si>
+    <t>resnet50_scratch_aug</t>
+  </si>
+  <si>
+    <t>resnet50_scratch_noaug</t>
+  </si>
+  <si>
+    <t>resnet50_transfer_aug</t>
+  </si>
+  <si>
+    <t>resnet50_transfer_noaug</t>
+  </si>
+  <si>
+    <t>swin_face_scratch_aug</t>
+  </si>
+  <si>
+    <t>vgg16_fine_tuning_aug</t>
+  </si>
+  <si>
+    <t>vgg16_fine_tuning_noaug</t>
+  </si>
+  <si>
+    <t>vgg16_transfer_aug</t>
+  </si>
+  <si>
+    <t>vgg16_transfer_noaug</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +239,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,2079 +533,2587 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>experiment_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>balanced_accuracy</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>precision_macro</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>recall_macro</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>f1_macro</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>precision_weighted</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>recall_weighted</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>f1_weighted</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>specificity_macro</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>top_2_accuracy</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>top_3_accuracy</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>mcc</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>cohen_kappa</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>auc_macro_ovr</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inference_total_seconds</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inference_ms_per_image</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>num_parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>custom_cnn_fine_tuning_aug</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
         <v>0.1786179921773142</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.156329131398181</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.1987978456196117</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.156329131398181</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.1181077704998267</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.3702147732138609</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.1786179921773142</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.1324828464695062</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0.8590510678728858</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.3259452411994785</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.4670795306388526</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.0157475656660686</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0.0132698874100325</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>0.572591695508273</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>18.63387749996036</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>6.073623696206115</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2">
         <v>1309415</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>custom_cnn_fine_tuning_noaug</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
         <v>0.2089308996088657</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0.1512383828696819</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.1622496527877384</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.1512383828696819</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.1353340552337263</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.2794961384152123</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0.2089308996088657</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>0.2164864752353209</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0.8617568894320516</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.4044980443285528</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.5453063885267275</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.028528243831716</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0.0266109373837766</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>0.5556061796601026</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>12.24374059960246</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>3.990788982921272</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3">
         <v>1309415</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>custom_cnn_scratch_aug</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
         <v>0.3161668839634941</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.3059592205802398</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.2792817395124898</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.3059592205802398</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.252615539439913</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.4096195904700754</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0.3161668839634941</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>0.323719387997656</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>0.8824850962701254</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.508148631029987</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>0.6646023468057366</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>0.1719229247717055</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>0.1626114668243091</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>0.6842718846865392</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>16.65500470018014</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>5.428619524178665</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4">
         <v>1309415</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>custom_cnn_scratch_noaug</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5">
         <v>0.5912646675358539</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.5252972799215873</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.4898816599613485</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.5252972799215873</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.4891331822287024</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.6407639523710599</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.5912646675358539</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>0.6096265656810076</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.9295655276516356</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.7728161668839635</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>0.863102998696219</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>0.4805267605702293</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>0.4776348620337998</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>0.8612790372921691</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>18.69433550024405</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>6.09332969369102</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5">
         <v>1309415</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>custom_cnn_transfer_aug</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
         <v>0.3207301173402868</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.3841243220267833</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.3756028070499307</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.3841243220267833</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.3171531316198389</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.5443555269622825</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0.3207301173402868</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>0.3280316772072827</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0.8897122544653275</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.4996740547588005</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0.644393741851369</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>0.2306654320662044</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.211511415964345</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>0.7624740622331798</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>17.70012599974871</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>5.769271838249252</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6">
         <v>1309415</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>custom_cnn_transfer_noaug</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
         <v>0.2503259452411995</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.2671871142763296</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.2189706694110326</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.2671871142763296</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.203678803741768</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.336132627550371</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0.2503259452411995</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>0.2704334584191066</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>0.8727143544753015</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>0.4335071707953064</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>0.5935462842242504</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>0.1006507676214166</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>0.09610963609587091</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>0.6272653626404916</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>17.61751920031384</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>5.742346545082737</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7">
         <v>1309415</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>densenet121_fine_tuning_aug</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:18">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
         <v>0.7578226857887875</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>0.723678586582932</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.6592981731438917</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.723678586582932</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.6848174324338322</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.7851778582158403</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>0.7578226857887875</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>0.7650350140822223</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>0.9593253990254232</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>0.8930899608865711</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>0.9475228161668841</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>0.6938799423503783</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>0.6903136650051062</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>0.9473036330033526</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>18.98706000018865</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>6.18874185143046</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8">
         <v>7218567</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>densenet121_fine_tuning_noaug</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:18">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
         <v>0.6779661016949152</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>0.5935100470201513</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.5633458445820752</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.5935100470201513</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.5751445738259836</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>0.6938776380408589</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>0.6779661016949152</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>0.6824036394887307</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>0.9439971097504204</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>0.8357235984354628</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>0.9142764015645372</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>0.5859697378589916</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>0.58424386766069</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>0.8918220299641781</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>17.7058238000609</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>5.771129009146317</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9">
         <v>7218567</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>densenet121_scratch_aug</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:18">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10">
         <v>0.6029986962190352</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0.617878383706573</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.534770002832088</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.617878383706573</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0.5437574548139618</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>0.7127087125579868</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>0.6029986962190352</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>0.6306501091656577</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>0.9355766726243656</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>0.7894393741851369</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>0.8872229465449805</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>0.5245865471380928</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>0.512363415850932</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>0.909655739012208</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>17.36335480026901</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>5.659502868405804</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10">
         <v>7218567</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>densenet121_scratch_noaug</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:18">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11">
         <v>0.7011082138200783</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>0.643815866035865</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.5924888327339913</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.643815866035865</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.610850561202021</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.7293367557623859</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>0.7011082138200783</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>0.7114390861789313</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>0.9489489864507884</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>0.8679921773142112</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>0.9390482398956976</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>0.6175527547431733</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>0.6158150552218166</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>0.92064853762931</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>17.69074649969116</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>5.766214634840665</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11">
         <v>7218567</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>densenet121_transfer_aug</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:18">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12">
         <v>0.4449152542372881</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>0.4655421326061419</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.3943254006390526</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.4655421326061419</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0.3925555194122627</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.5724722579889979</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>0.4449152542372881</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>0.4615337756664451</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>0.9080352326858444</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>0.6427640156453716</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>0.7672750977835724</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>0.3443623332421628</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>0.3311573690212988</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>0.8116446042165932</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>17.55205800011754</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>5.721009778395548</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12">
         <v>7218567</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>densenet121_transfer_noaug</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13">
         <v>0.4726205997392438</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>0.4660914249211932</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.4008747521815684</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.4660914249211932</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.3980171376135838</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>0.57290326290862</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>0.4726205997392438</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>0.4953382029943929</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>0.9113123577081382</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>0.6613428943937418</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>0.7894393741851369</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>0.3606589156360994</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13">
         <v>0.3514782670496114</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13">
         <v>0.8222602431880291</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>18.03880260000005</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13">
         <v>5.879661864406797</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13">
         <v>7218567</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>efficientnetb0_fine_tuning_aug</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
         <v>0.6659061277705346</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>0.670478297876189</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.579328040350866</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.670478297876189</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.6040895289494135</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>0.734207093879932</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>0.6659061277705346</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>0.6788708777808787</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>0.9446483580259368</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>0.833767926988266</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>0.9051499348109516</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>0.5924606383327132</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14">
         <v>0.5829669856046893</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14">
         <v>0.922747073749263</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>12.03476000018418</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>3.922672751037868</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14">
         <v>4337795</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>efficientnetb0_fine_tuning_noaug</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
         <v>0.7001303780964798</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>0.6500586072440625</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>0.5983826230459593</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.6500586072440625</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.6182810424222965</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>0.729552836448851</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>0.7001303780964798</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>0.7099567621384165</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>0.9489674932096422</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>0.8761408083441982</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>0.9413298565840938</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>0.6185855278116552</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>0.6160961707274146</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15">
         <v>0.9229887350130042</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15">
         <v>11.26820140006021</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>3.672816623226925</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15">
         <v>4337795</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>efficientnetb0_scratch_aug</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
         <v>0.4667535853976532</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.3493121177704617</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.3518307409130409</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.3493121177704617</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>0.3253184162056949</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>0.4655621295605673</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>0.4667535853976532</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>0.4432713862514245</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>0.9038374533175232</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>0.5945241199478487</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>0.7310951760104303</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>0.3093787761519264</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>0.3023175839669132</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>0.7361596418255366</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16">
         <v>11.3054363001138</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16">
         <v>3.684953161705931</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16">
         <v>4337795</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>efficientnetb0_scratch_noaug</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
         <v>0.64374185136897</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>0.6111233175221024</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>0.566959638518503</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.6111233175221024</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0.5695201104259009</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>0.7150586258972991</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>0.64374185136897</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>0.6686919709435322</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>0.9406116220292102</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>0.8393089960886571</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>0.9159061277705346</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>0.5569961967123923</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>0.5502863512690006</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>0.9066106854457257</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>11.06104899989441</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17">
         <v>3.605296284189834</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17">
         <v>4337795</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>efficientnetb0_transfer_aug</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
         <v>0.3624511082138201</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>0.4129312497161234</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.3539506353501814</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.4129312497161234</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>0.3235836382226749</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>0.5477637931884098</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>0.3624511082138201</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>0.3704192486574073</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>0.8954504454154977</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>0.5697522816166884</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>0.7089308996088657</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>0.2635599349946482</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18">
         <v>0.2476006252893117</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18">
         <v>0.7679937122036921</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18">
         <v>11.00259880023077</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18">
         <v>3.586244719762312</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18">
         <v>4337795</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>efficientnetb0_transfer_noaug</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:18">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19">
         <v>0.4559973924380704</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>0.4576837630732376</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>0.3994451212974924</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.4576837630732376</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.3877334502577053</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>0.5775971523952852</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>0.4559973924380704</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>0.4886258290752512</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>0.9100064760250278</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>0.6499348109517601</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>0.7868318122555411</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>0.3481762283305381</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19">
         <v>0.3383147073467534</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19">
         <v>0.803171930739034</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19">
         <v>11.47146539995447</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19">
         <v>3.739069556699631</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R19">
         <v>4337795</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>mobilenetv2_fine_tuning_aug</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20">
         <v>0.5961538461538461</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>0.5865349146462887</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>0.5171046386052794</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.5865349146462887</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.5339900243346591</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>0.6731300288614633</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>0.5961538461538461</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>0.6103049794683783</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>0.932214903689608</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>0.7770534550195567</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>0.8683181225554107</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>0.5068676810591211</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20">
         <v>0.4970210296372718</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20">
         <v>0.889592706189093</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20">
         <v>10.77044880017638</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20">
         <v>3.510576532000125</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R20">
         <v>2554119</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>mobilenetv2_fine_tuning_noaug</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:18">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21">
         <v>0.5941981747066493</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>0.5583650858533168</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>0.5038060883436871</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.5583650858533168</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>0.5209256330653265</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>0.6393525610904481</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>0.5941981747066493</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>0.6079714117031114</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>0.9303871180132964</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>0.7855280312907431</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>0.8911342894393742</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>0.4908030892165078</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21">
         <v>0.4868545832733826</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21">
         <v>0.866921433043861</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21">
         <v>10.83135299989954</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21">
         <v>3.530427966068949</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R21">
         <v>2554119</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>mobilenetv2_scratch_aug</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:18">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22">
         <v>0.6890482398956975</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>0.6722780044367028</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>0.5907597293118647</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.6722780044367028</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>0.6006777527269732</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>0.7544866957949942</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>0.6890482398956975</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>0.7054980097227055</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>0.9487276348618624</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>0.8484354628422425</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>0.9191655801825294</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>0.6124448137879988</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22">
         <v>0.6063081156399091</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22">
         <v>0.9302423130541292</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22">
         <v>11.00819520000368</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22">
         <v>3.588068839636142</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22">
         <v>2554119</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>mobilenetv2_scratch_noaug</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:18">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23">
         <v>0.7213168187744459</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>0.6469471599964277</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.6234740707120742</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.6469471599964277</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0.6309965909240226</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>0.7452273068357531</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>0.7213168187744459</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>0.729989201916133</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>0.9522568880599966</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>0.8865710560625815</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>0.9458930899608866</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>0.6423931654304367</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23">
         <v>0.640635182801167</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23">
         <v>0.9297445520533232</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23">
         <v>10.91634969972074</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23">
         <v>3.558132235893331</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R23">
         <v>2554119</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>mobilenetv2_transfer_aug</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:18">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24">
         <v>0.3911342894393741</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>0.4223553019733459</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.3512637900643305</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.4223553019733459</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>0.3417691945628772</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>0.5290321231109664</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>0.3911342894393741</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>0.4148528718017805</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>0.8997435169999736</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>0.5948500651890483</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>0.734354628422425</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>0.2840737953319375</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24">
         <v>0.2724699649159599</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24">
         <v>0.7700848906700817</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24">
         <v>10.64004430035129</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24">
         <v>3.468071805851138</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R24">
         <v>2554119</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mobilenetv2_transfer_noaug</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:18">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25">
         <v>0.4253585397653194</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>0.4322454200112866</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.3678682884898875</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.4322454200112866</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>0.3608906925026317</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>0.532873519960391</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>0.4253585397653194</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>0.4553105819873631</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>0.904232579570232</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>0.6277705345501956</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>0.7646675358539765</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>0.307826086168214</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25">
         <v>0.2996054190907131</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25">
         <v>0.7891707169539534</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25">
         <v>10.42558989999816</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25">
         <v>3.398171414601746</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R25">
         <v>2554119</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>resnet50_fine_tuning_aug</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:18">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26">
+        <v>0.4110169491525424</v>
+      </c>
+      <c r="C26">
+        <v>0.4754390904600467</v>
+      </c>
+      <c r="D26">
+        <v>0.454762051436004</v>
+      </c>
+      <c r="E26">
+        <v>0.4754390904600467</v>
+      </c>
+      <c r="F26">
+        <v>0.384605783920219</v>
+      </c>
+      <c r="G26">
+        <v>0.6118648323932968</v>
+      </c>
+      <c r="H26">
+        <v>0.4110169491525424</v>
+      </c>
+      <c r="I26">
+        <v>0.3744515134107242</v>
+      </c>
+      <c r="J26">
+        <v>0.9011020434095</v>
+      </c>
+      <c r="K26">
+        <v>0.5938722294654498</v>
+      </c>
+      <c r="L26">
+        <v>0.7398956975228161</v>
+      </c>
+      <c r="M26">
+        <v>0.3292605457306956</v>
+      </c>
+      <c r="N26">
+        <v>0.2980748157056992</v>
+      </c>
+      <c r="O26">
+        <v>0.8388568510690566</v>
+      </c>
+      <c r="P26">
+        <v>12.52515539992601</v>
+      </c>
+      <c r="Q26">
+        <v>4.082514797889833</v>
+      </c>
+      <c r="R26">
+        <v>28982206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27">
+        <v>0.85625814863103</v>
+      </c>
+      <c r="C27">
+        <v>0.7931707381717856</v>
+      </c>
+      <c r="D27">
+        <v>0.7925888003023297</v>
+      </c>
+      <c r="E27">
+        <v>0.7931707381717856</v>
+      </c>
+      <c r="F27">
+        <v>0.7917196133907467</v>
+      </c>
+      <c r="G27">
+        <v>0.8594116935737302</v>
+      </c>
+      <c r="H27">
+        <v>0.85625814863103</v>
+      </c>
+      <c r="I27">
+        <v>0.8574040094277918</v>
+      </c>
+      <c r="J27">
+        <v>0.9749416980341772</v>
+      </c>
+      <c r="K27">
+        <v>0.9449152542372882</v>
+      </c>
+      <c r="L27">
+        <v>0.9729465449804432</v>
+      </c>
+      <c r="M27">
+        <v>0.8116554089797412</v>
+      </c>
+      <c r="N27">
+        <v>0.8115192173394942</v>
+      </c>
+      <c r="O27">
+        <v>0.9646020363324924</v>
+      </c>
+      <c r="P27">
+        <v>12.5411926000379</v>
+      </c>
+      <c r="Q27">
+        <v>4.087742046948469</v>
+      </c>
+      <c r="R27">
+        <v>28982206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28">
+        <v>0.1525423728813559</v>
+      </c>
+      <c r="C28">
+        <v>0.2249143103758172</v>
+      </c>
+      <c r="D28">
+        <v>0.3184033561747213</v>
+      </c>
+      <c r="E28">
+        <v>0.2249143103758172</v>
+      </c>
+      <c r="F28">
+        <v>0.1277755798420829</v>
+      </c>
+      <c r="G28">
+        <v>0.4726137395440514</v>
+      </c>
+      <c r="H28">
+        <v>0.1525423728813559</v>
+      </c>
+      <c r="I28">
+        <v>0.1706946327156815</v>
+      </c>
+      <c r="J28">
+        <v>0.8678397393791014</v>
+      </c>
+      <c r="K28">
+        <v>0.2777053455019557</v>
+      </c>
+      <c r="L28">
+        <v>0.4491525423728814</v>
+      </c>
+      <c r="M28">
+        <v>0.0797597578550117</v>
+      </c>
+      <c r="N28">
+        <v>0.0622258217309721</v>
+      </c>
+      <c r="O28">
+        <v>0.6631841042335843</v>
+      </c>
+      <c r="P28">
+        <v>7.3847628000658</v>
+      </c>
+      <c r="Q28">
+        <v>2.407028292068384</v>
+      </c>
+      <c r="R28">
+        <v>11920711</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29">
+        <v>0.3803780964797913</v>
+      </c>
+      <c r="C29">
+        <v>0.45270442243426</v>
+      </c>
+      <c r="D29">
+        <v>0.4547510441654983</v>
+      </c>
+      <c r="E29">
+        <v>0.45270442243426</v>
+      </c>
+      <c r="F29">
+        <v>0.3610963289364997</v>
+      </c>
+      <c r="G29">
+        <v>0.628166457278204</v>
+      </c>
+      <c r="H29">
+        <v>0.3803780964797913</v>
+      </c>
+      <c r="I29">
+        <v>0.3610881895487959</v>
+      </c>
+      <c r="J29">
+        <v>0.8984007770320507</v>
+      </c>
+      <c r="K29">
+        <v>0.5941981747066493</v>
+      </c>
+      <c r="L29">
+        <v>0.7464146023468058</v>
+      </c>
+      <c r="M29">
+        <v>0.31448756099555</v>
+      </c>
+      <c r="N29">
+        <v>0.2739236275459124</v>
+      </c>
+      <c r="O29">
+        <v>0.8329209934984636</v>
+      </c>
+      <c r="P29">
+        <v>12.59075049986132</v>
+      </c>
+      <c r="Q29">
+        <v>4.10389520855975</v>
+      </c>
+      <c r="R29">
+        <v>28982206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30">
+        <v>0.3745110821382008</v>
+      </c>
+      <c r="C30">
+        <v>0.4584381848385843</v>
+      </c>
+      <c r="D30">
+        <v>0.4311465790850469</v>
+      </c>
+      <c r="E30">
+        <v>0.4584381848385843</v>
+      </c>
+      <c r="F30">
+        <v>0.3425900413010591</v>
+      </c>
+      <c r="G30">
+        <v>0.6116341236837948</v>
+      </c>
+      <c r="H30">
+        <v>0.3745110821382008</v>
+      </c>
+      <c r="I30">
+        <v>0.3273678571131684</v>
+      </c>
+      <c r="J30">
+        <v>0.8967387924009131</v>
+      </c>
+      <c r="K30">
+        <v>0.5534550195567145</v>
+      </c>
+      <c r="L30">
+        <v>0.6968709256844851</v>
+      </c>
+      <c r="M30">
+        <v>0.3041456641648934</v>
+      </c>
+      <c r="N30">
+        <v>0.2676915391919582</v>
+      </c>
+      <c r="O30">
+        <v>0.8327178844920707</v>
+      </c>
+      <c r="P30">
+        <v>15.9204692998901</v>
+      </c>
+      <c r="Q30">
+        <v>5.189201205961572</v>
+      </c>
+      <c r="R30">
+        <v>41223870</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31">
+        <v>0.2385919165580182</v>
+      </c>
+      <c r="C31">
+        <v>0.3034262990234907</v>
+      </c>
+      <c r="D31">
+        <v>0.355979941305505</v>
+      </c>
+      <c r="E31">
+        <v>0.3034262990234907</v>
+      </c>
+      <c r="F31">
+        <v>0.2120190699261663</v>
+      </c>
+      <c r="G31">
+        <v>0.5313536201393969</v>
+      </c>
+      <c r="H31">
+        <v>0.2385919165580182</v>
+      </c>
+      <c r="I31">
+        <v>0.2219081126470259</v>
+      </c>
+      <c r="J31">
+        <v>0.8777951702917131</v>
+      </c>
+      <c r="K31">
+        <v>0.3852672750977836</v>
+      </c>
+      <c r="L31">
+        <v>0.5003259452411994</v>
+      </c>
+      <c r="M31">
+        <v>0.1601374719779031</v>
+      </c>
+      <c r="N31">
+        <v>0.1345129663382769</v>
+      </c>
+      <c r="O31">
+        <v>0.6968708645889757</v>
+      </c>
+      <c r="P31">
+        <v>7.595480599906295</v>
+      </c>
+      <c r="Q31">
+        <v>2.475710756162417</v>
+      </c>
+      <c r="R31">
+        <v>12360775</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32">
+        <v>0.8490873533246415</v>
+      </c>
+      <c r="C32">
+        <v>0.781336617101268</v>
+      </c>
+      <c r="D32">
+        <v>0.7739506170134681</v>
+      </c>
+      <c r="E32">
+        <v>0.781336617101268</v>
+      </c>
+      <c r="F32">
+        <v>0.7769769282906492</v>
+      </c>
+      <c r="G32">
+        <v>0.8521666369553755</v>
+      </c>
+      <c r="H32">
+        <v>0.8490873533246415</v>
+      </c>
+      <c r="I32">
+        <v>0.8500015030721535</v>
+      </c>
+      <c r="J32">
+        <v>0.9739774853405559</v>
+      </c>
+      <c r="K32">
+        <v>0.9429595827900912</v>
+      </c>
+      <c r="L32">
+        <v>0.967405475880052</v>
+      </c>
+      <c r="M32">
+        <v>0.8028326950883955</v>
+      </c>
+      <c r="N32">
+        <v>0.8025313253070669</v>
+      </c>
+      <c r="O32">
+        <v>0.957537439931388</v>
+      </c>
+      <c r="P32">
+        <v>13.10840779985301</v>
+      </c>
+      <c r="Q32">
+        <v>4.272623142064215</v>
+      </c>
+      <c r="R32">
+        <v>41223870</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33">
+        <v>0.2894393741851369</v>
+      </c>
+      <c r="C33">
+        <v>0.1792310727154026</v>
+      </c>
+      <c r="D33">
+        <v>0.2810780276626155</v>
+      </c>
+      <c r="E33">
+        <v>0.1792310727154026</v>
+      </c>
+      <c r="F33">
+        <v>0.1682116357241706</v>
+      </c>
+      <c r="G33">
+        <v>0.32628331661462</v>
+      </c>
+      <c r="H33">
+        <v>0.2894393741851369</v>
+      </c>
+      <c r="I33">
+        <v>0.2577335934185735</v>
+      </c>
+      <c r="J33">
+        <v>0.8581974338304175</v>
+      </c>
+      <c r="K33">
+        <v>0.39374185136897</v>
+      </c>
+      <c r="L33">
+        <v>0.4996740547588005</v>
+      </c>
+      <c r="M33">
+        <v>0.0124139376023529</v>
+      </c>
+      <c r="N33">
+        <v>0.0118752436796929</v>
+      </c>
+      <c r="O33">
+        <v>0.5367736010463792</v>
+      </c>
+      <c r="P33">
+        <v>7.408541599987075</v>
+      </c>
+      <c r="Q33">
+        <v>2.414778878744157</v>
+      </c>
+      <c r="R33">
+        <v>12360775</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34">
+        <v>0.3875488917861799</v>
+      </c>
+      <c r="C34">
+        <v>0.4719430342099645</v>
+      </c>
+      <c r="D34">
+        <v>0.4162989618054342</v>
+      </c>
+      <c r="E34">
+        <v>0.4719430342099645</v>
+      </c>
+      <c r="F34">
+        <v>0.3373378797113912</v>
+      </c>
+      <c r="G34">
+        <v>0.595159994842938</v>
+      </c>
+      <c r="H34">
+        <v>0.3875488917861799</v>
+      </c>
+      <c r="I34">
+        <v>0.3414363082999385</v>
+      </c>
+      <c r="J34">
+        <v>0.8984305610147666</v>
+      </c>
+      <c r="K34">
+        <v>0.559973924380704</v>
+      </c>
+      <c r="L34">
+        <v>0.665580182529335</v>
+      </c>
+      <c r="M34">
+        <v>0.3067888561332322</v>
+      </c>
+      <c r="N34">
+        <v>0.2790225535417275</v>
+      </c>
+      <c r="O34">
+        <v>0.8450109561456541</v>
+      </c>
+      <c r="P34">
+        <v>13.11951460014097</v>
+      </c>
+      <c r="Q34">
+        <v>4.276243350763029</v>
+      </c>
+      <c r="R34">
+        <v>41223870</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35">
+        <v>0.1701434159061277</v>
+      </c>
+      <c r="C35">
+        <v>0.2651944446450779</v>
+      </c>
+      <c r="D35">
+        <v>0.3177524377795655</v>
+      </c>
+      <c r="E35">
+        <v>0.2651944446450779</v>
+      </c>
+      <c r="F35">
+        <v>0.1671010825922564</v>
+      </c>
+      <c r="G35">
+        <v>0.4890238665852359</v>
+      </c>
+      <c r="H35">
+        <v>0.1701434159061277</v>
+      </c>
+      <c r="I35">
+        <v>0.1706392849664546</v>
+      </c>
+      <c r="J35">
+        <v>0.8713986727315559</v>
+      </c>
+      <c r="K35">
+        <v>0.3282268578878748</v>
+      </c>
+      <c r="L35">
+        <v>0.4491525423728814</v>
+      </c>
+      <c r="M35">
+        <v>0.1155294122170307</v>
+      </c>
+      <c r="N35">
+        <v>0.0900163109369486</v>
+      </c>
+      <c r="O35">
+        <v>0.6682005000855026</v>
+      </c>
+      <c r="P35">
+        <v>7.425835100002587</v>
+      </c>
+      <c r="Q35">
+        <v>2.420415612777897</v>
+      </c>
+      <c r="R35">
+        <v>12360775</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36">
         <v>0.6792698826597132</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C36">
         <v>0.643225189152134</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D36">
         <v>0.5945232281570626</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E36">
         <v>0.643225189152134</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F36">
         <v>0.6068040434647649</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G36">
         <v>0.7329566537259022</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H36">
         <v>0.6792698826597132</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I36">
         <v>0.6879427044113163</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J36">
         <v>0.9459240541891346</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K36">
         <v>0.8399608865710561</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L36">
         <v>0.9194915254237288</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M36">
         <v>0.6039988405431983</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N36">
         <v>0.5950128924877465</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O36">
         <v>0.9147736704242666</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P36">
         <v>16.26315889973193</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q36">
         <v>5.300899250238571</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R36">
         <v>24034887</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>resnet50_fine_tuning_noaug</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="37" spans="1:18">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37">
         <v>0.5873533246414603</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C37">
         <v>0.5371213221658285</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D37">
         <v>0.4904286591959802</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E37">
         <v>0.5371213221658285</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F37">
         <v>0.5048233576818101</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G37">
         <v>0.6328150217103934</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H37">
         <v>0.5873533246414603</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I37">
         <v>0.6031640299750168</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J37">
         <v>0.9291336261671804</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K37">
         <v>0.7633637548891786</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L37">
         <v>0.8595176010430248</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M37">
         <v>0.479913845615882</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N37">
         <v>0.4767141030841778</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O37">
         <v>0.8489150622223169</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P37">
         <v>16.24742299970239</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q37">
         <v>5.295770208507951</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R37">
         <v>24034887</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>resnet50_scratch_aug</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="38" spans="1:18">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38">
         <v>0.4491525423728814</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C38">
         <v>0.4543529280691438</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D38">
         <v>0.3937450956697569</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E38">
         <v>0.4543529280691438</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F38">
         <v>0.3721530342942617</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G38">
         <v>0.5948986702311608</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H38">
         <v>0.4491525423728814</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I38">
         <v>0.4809455185904923</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J38">
         <v>0.9115539134962436</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K38">
         <v>0.6271186440677966</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L38">
         <v>0.7750977835723598</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M38">
         <v>0.352959646857224</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N38">
         <v>0.3373609458925458</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O38">
         <v>0.8110730995944427</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P38">
         <v>16.34766810014844</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q38">
         <v>5.328444621951904</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R38">
         <v>24034887</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>resnet50_scratch_noaug</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="39" spans="1:18">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39">
         <v>0.636245110821382</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C39">
         <v>0.5797036668285271</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D39">
         <v>0.5218055632115122</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E39">
         <v>0.5797036668285271</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F39">
         <v>0.53677441219436</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G39">
         <v>0.6729142450985156</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H39">
         <v>0.636245110821382</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I39">
         <v>0.646499628090508</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J39">
         <v>0.9379218745627742</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K39">
         <v>0.8210560625814863</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L39">
         <v>0.9097131681877444</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M39">
         <v>0.5391692306307432</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N39">
         <v>0.5357702486517034</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O39">
         <v>0.8961244019695787</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P39">
         <v>16.37335819983855</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q39">
         <v>5.336818187691835</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R39">
         <v>24034887</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>resnet50_transfer_aug</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="40" spans="1:18">
+      <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40">
         <v>0.4005867014341591</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C40">
         <v>0.4332363596154999</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D40">
         <v>0.3708999286179404</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E40">
         <v>0.4332363596154999</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F40">
         <v>0.3585935546523722</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G40">
         <v>0.5517234921973768</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H40">
         <v>0.4005867014341591</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I40">
         <v>0.4160498952295143</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J40">
         <v>0.901184574325228</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K40">
         <v>0.6117992177314211</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L40">
         <v>0.7486962190352021</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M40">
         <v>0.2997230640281031</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N40">
         <v>0.2855620796764417</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O40">
         <v>0.7869376721122362</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P40">
         <v>16.23840310005471</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q40">
         <v>5.292830215141692</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R40">
         <v>24034887</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>resnet50_transfer_noaug</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+    <row r="41" spans="1:18">
+      <c r="A41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41">
         <v>0.4178617992177314</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C41">
         <v>0.4345763930174395</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D41">
         <v>0.3760853083314475</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E41">
         <v>0.4345763930174395</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F41">
         <v>0.3558152950858418</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G41">
         <v>0.5514507259612155</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H41">
         <v>0.4178617992177314</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I41">
         <v>0.4541963920018414</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J41">
         <v>0.9043282452650708</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K41">
         <v>0.6183181225554107</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L41">
         <v>0.7516297262059974</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M41">
         <v>0.3091390156754151</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N41">
         <v>0.2981458937910908</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O41">
         <v>0.7888740116139713</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P41">
         <v>16.2533809999004</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q41">
         <v>5.297712190319556</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R41">
         <v>24034887</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>vgg16_fine_tuning_aug</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+    <row r="42" spans="1:18">
+      <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42">
+        <v>0.6939374185136897</v>
+      </c>
+      <c r="C42">
+        <v>0.6307741969559878</v>
+      </c>
+      <c r="D42">
+        <v>0.5883579475239648</v>
+      </c>
+      <c r="E42">
+        <v>0.6307741969559878</v>
+      </c>
+      <c r="F42">
+        <v>0.6039919648153156</v>
+      </c>
+      <c r="G42">
+        <v>0.7051295212562448</v>
+      </c>
+      <c r="H42">
+        <v>0.6939374185136897</v>
+      </c>
+      <c r="I42">
+        <v>0.6975108018639268</v>
+      </c>
+      <c r="J42">
+        <v>0.9460432650328642</v>
+      </c>
+      <c r="K42">
+        <v>0.8634289439374185</v>
+      </c>
+      <c r="L42">
+        <v>0.9305736636245112</v>
+      </c>
+      <c r="M42">
+        <v>0.6018364705916449</v>
+      </c>
+      <c r="N42">
+        <v>0.601265276158397</v>
+      </c>
+      <c r="O42">
+        <v>0.9076709200167292</v>
+      </c>
+      <c r="P42">
+        <v>26.66923970007338</v>
+      </c>
+      <c r="Q42">
+        <v>8.692711766647125</v>
+      </c>
+      <c r="R42">
+        <v>38800289</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43">
         <v>0.758148631029987</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C43">
         <v>0.7273510902404586</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D43">
         <v>0.6529592521060146</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E43">
         <v>0.7273510902404586</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F43">
         <v>0.6805044895323402</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G43">
         <v>0.7940223109951007</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H43">
         <v>0.758148631029987</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I43">
         <v>0.7673373958147501</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J43">
         <v>0.959892780250853</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K43">
         <v>0.9015645371577576</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L43">
         <v>0.9511082138200784</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M43">
         <v>0.6969141079835205</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N43">
         <v>0.6922252000574867</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O43">
         <v>0.9516821300920816</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P43">
         <v>25.95941670006141</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q43">
         <v>8.461348337699286</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R43">
         <v>21139783</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>vgg16_fine_tuning_noaug</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
+    <row r="44" spans="1:18">
+      <c r="A44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44">
         <v>0.7770534550195567</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C44">
         <v>0.69799381999935</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D44">
         <v>0.6900734814949951</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E44">
         <v>0.69799381999935</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F44">
         <v>0.6920464773743514</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G44">
         <v>0.7850752351451366</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H44">
         <v>0.7770534550195567</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I44">
         <v>0.7793796653620726</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J44">
         <v>0.9611614814612224</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K44">
         <v>0.9149282920469362</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L44">
         <v>0.9582790091264668</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M44">
         <v>0.7105078995584945</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N44">
         <v>0.7095589237700684</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O44">
         <v>0.9433436182498914</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P44">
         <v>25.53423920040951</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q44">
         <v>8.322763755022654</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R44">
         <v>21139783</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>vgg16_transfer_aug</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
+    <row r="45" spans="1:18">
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45">
         <v>0.5909387222946545</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C45">
         <v>0.589735634703298</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D45">
         <v>0.51323129578194</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E45">
         <v>0.589735634703298</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F45">
         <v>0.5249424310148872</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G45">
         <v>0.6886205829116288</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H45">
         <v>0.5909387222946545</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I45">
         <v>0.6145731531355595</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J45">
         <v>0.9328543699652262</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K45">
         <v>0.7809647979139505</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L45">
         <v>0.8771186440677966</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M45">
         <v>0.5061125149397387</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N45">
         <v>0.4954802296161547</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O45">
         <v>0.8825744180517848</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P45">
         <v>25.66863289987668</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q45">
         <v>8.366568741811175</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R45">
         <v>21139783</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>vgg16_transfer_noaug</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+    <row r="46" spans="1:18">
+      <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46">
         <v>0.6245110821382008</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C46">
         <v>0.5949795876880815</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D46">
         <v>0.5257938822931391</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E46">
         <v>0.5949795876880815</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F46">
         <v>0.5383805526288513</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G46">
         <v>0.6872313918070557</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H46">
         <v>0.6245110821382008</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I46">
         <v>0.644970850757739</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J46">
         <v>0.9368444002752054</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K46">
         <v>0.788787483702738</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L46">
         <v>0.8836375488917861</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M46">
         <v>0.5312038637649076</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N46">
         <v>0.5264398698114823</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O46">
         <v>0.8913816415689206</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P46">
         <v>26.26858030026778</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q46">
         <v>8.562118741938651</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R46">
         <v>21139783</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>